--- a/public/templates/Item_sample_template.xlsx
+++ b/public/templates/Item_sample_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>S.No</t>
   </si>
@@ -35,16 +35,16 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Sub-Category</t>
+    <t>Group</t>
   </si>
   <si>
     <t>Sub-Type</t>
   </si>
   <si>
     <t>Item Name</t>
+  </si>
+  <si>
+    <t>Item Code</t>
   </si>
   <si>
     <t>HSN/SAC</t>
@@ -325,10 +325,7 @@
 S - for Service</t>
   </si>
   <si>
-    <t>Category of the Item</t>
-  </si>
-  <si>
-    <t>Sub Category of the item</t>
+    <t>Group of the item</t>
   </si>
   <si>
     <t>FG - for Finished Goods 
@@ -343,6 +340,9 @@
     <t>Name of the Item</t>
   </si>
   <si>
+    <t>Mandatory if manual code is being used</t>
+  </si>
+  <si>
     <t>HSN/SAC Code</t>
   </si>
   <si>
@@ -366,9 +366,6 @@
   </si>
   <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>Shoe</t>
   </si>
   <si>
     <t>Sports</t>
@@ -1074,7 +1071,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1092,9 +1089,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1157,21 +1151,21 @@
   <dxfs count="19">
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1395,6 +1389,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1660,11 +1661,10 @@
   <cols>
     <col min="1" max="1" width="9.57142857142857" customWidth="1"/>
     <col min="2" max="2" width="13.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="23.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="24.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="26.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="17.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="15.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="26.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="17.8571428571429" customWidth="1"/>
+    <col min="6" max="7" width="15.2857142857143" customWidth="1"/>
     <col min="8" max="8" width="16.7142857142857" customWidth="1"/>
     <col min="9" max="10" width="12.5714285714286" customWidth="1"/>
     <col min="44" max="44" width="21" customWidth="1"/>
@@ -1706,253 +1706,253 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AH1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AK1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AL1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="AN1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AS1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AT1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AU1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AV1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="AW1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="7" t="s">
+      <c r="AX1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="7" t="s">
+      <c r="AY1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="7" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="7" t="s">
+      <c r="BA1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="BB1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="7" t="s">
+      <c r="BC1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="7" t="s">
+      <c r="BD1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BE1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BF1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="7" t="s">
+      <c r="BG1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BH1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BI1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BK1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BL1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BM1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BN1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BO1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="7" t="s">
+      <c r="BP1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="7" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="7" t="s">
+      <c r="BR1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="7" t="s">
+      <c r="BS1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="7" t="s">
+      <c r="BT1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="7" t="s">
+      <c r="BU1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="7" t="s">
+      <c r="BV1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="7" t="s">
+      <c r="BW1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="7" t="s">
+      <c r="BX1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="7" t="s">
+      <c r="BY1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="7" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="7" t="s">
+      <c r="CA1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="7" t="s">
+      <c r="CB1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="7" t="s">
+      <c r="CC1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="7" t="s">
+      <c r="CD1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="7" t="s">
+      <c r="CE1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="7" t="s">
+      <c r="CF1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="7" t="s">
+      <c r="CG1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="7" t="s">
+      <c r="CH1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="7" t="s">
+      <c r="CI1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="7" t="s">
+      <c r="CJ1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="7" t="s">
+      <c r="CK1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="7" t="s">
+      <c r="CL1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="7" t="s">
+      <c r="CM1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="7" t="s">
+      <c r="CN1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="7" t="s">
+      <c r="CO1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="7" t="s">
+      <c r="CP1" s="6" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1960,28 +1960,28 @@
       <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J2" s="6"/>
+      <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -2020,20 +2020,20 @@
       <c r="AR2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="AS2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AT2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AU2" s="6"/>
-      <c r="AV2" s="6"/>
-      <c r="AW2" s="6"/>
-      <c r="AX2" s="8"/>
-      <c r="AY2" s="6"/>
-      <c r="AZ2" s="6"/>
-      <c r="BA2" s="6"/>
-      <c r="BB2" s="8"/>
+      <c r="AU2" s="2"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2"/>
+      <c r="AX2" s="7"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="7"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:49">
       <c r="A3" s="3">
@@ -2051,46 +2051,43 @@
       <c r="E3" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="G3" s="3">
         <v>94042910</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR3" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AS3" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AT3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AU3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AU3" s="3" t="s">
+      <c r="AV3" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AW3" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="E2:F2">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/templates/Item_sample_template.xlsx
+++ b/public/templates/Item_sample_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
   <si>
     <t>S.No</t>
   </si>
@@ -41,6 +41,15 @@
     <t>Sub-Type</t>
   </si>
   <si>
+    <t>Asset Category</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Model No</t>
+  </si>
+  <si>
     <t>Item Name</t>
   </si>
   <si>
@@ -81,6 +90,15 @@
   </si>
   <si>
     <t>Shelf Life (Days)</t>
+  </si>
+  <si>
+    <t>Expected Life (yrs)</t>
+  </si>
+  <si>
+    <t>Maintenance Schedule</t>
+  </si>
+  <si>
+    <t>Brand Name</t>
   </si>
   <si>
     <t>Alternate UOM 1</t>
@@ -335,6 +353,15 @@
 A  - for Asset
 E  - for Expense
 Leave blank in case of service</t>
+  </si>
+  <si>
+    <t>Asset Category is mandatory when the Sub Type is an asset</t>
+  </si>
+  <si>
+    <t>Brand is mandatory when the Sub Type is an asset.</t>
+  </si>
+  <si>
+    <t>Model No. is mandatory when the Sub Type is an asset.</t>
   </si>
   <si>
     <t>Name of the Item</t>
@@ -575,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,6 +618,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -947,7 +980,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -971,16 +1004,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -989,89 +1022,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1091,6 +1124,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1391,13 +1427,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1656,23 +1685,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CP3"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:DF3"/>
+  <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="9.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="13.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="26.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="17.8571428571429" customWidth="1"/>
-    <col min="6" max="7" width="15.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="16.7142857142857" customWidth="1"/>
-    <col min="9" max="10" width="12.5714285714286" customWidth="1"/>
-    <col min="44" max="44" width="21" customWidth="1"/>
-    <col min="45" max="45" width="17" customWidth="1"/>
-    <col min="48" max="48" width="16.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.57407407407407" customWidth="1"/>
+    <col min="2" max="2" width="13.4259259259259" customWidth="1"/>
+    <col min="3" max="3" width="24.287037037037" customWidth="1"/>
+    <col min="4" max="4" width="26.1388888888889" customWidth="1"/>
+    <col min="5" max="8" width="17.8611111111111" customWidth="1"/>
+    <col min="9" max="10" width="15.287037037037" customWidth="1"/>
+    <col min="11" max="11" width="16.712962962963" customWidth="1"/>
+    <col min="12" max="13" width="12.5740740740741" customWidth="1"/>
+    <col min="52" max="52" width="21" customWidth="1"/>
+    <col min="53" max="53" width="17" customWidth="1"/>
+    <col min="56" max="56" width="16.4259259259259" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:94">
+    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:108">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1706,7 +1735,7 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
@@ -1715,369 +1744,385 @@
       <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="W1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AB1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AC1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AD1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AE1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AG1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AH1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AI1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AK1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AL1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AM1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AN1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AO1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AP1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AR1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AS1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AT1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AU1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AV1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AW1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AX1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AY1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="BA1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BB1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BC1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BD1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BE1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BF1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BG1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BH1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BI1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BK1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BL1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BM1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BN1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BO1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BP1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BR1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BS1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BT1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BU1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BV1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BW1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BX1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BY1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BZ1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CA1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CB1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CC1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="6" t="s">
+      <c r="CD1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="6" t="s">
+      <c r="CE1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="6" t="s">
+      <c r="CF1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="6" t="s">
+      <c r="CG1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="6" t="s">
+      <c r="CH1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="6" t="s">
+      <c r="CI1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="6" t="s">
+      <c r="CJ1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="6" t="s">
+      <c r="CK1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="6" t="s">
+      <c r="CL1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="6" t="s">
+      <c r="CM1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="6" t="s">
+      <c r="CN1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="6" t="s">
+      <c r="CO1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="6" t="s">
+      <c r="CP1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="6" t="s">
+      <c r="CQ1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="6" t="s">
+      <c r="CR1" s="7" t="s">
         <v>93</v>
       </c>
+      <c r="CS1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="CT1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="CU1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="CV1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="CW1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CX1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="CY1" s="3"/>
+      <c r="CZ1" s="3"/>
+      <c r="DA1" s="3"/>
+      <c r="DB1" s="3"/>
+      <c r="DC1" s="3"/>
+      <c r="DD1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:54">
+    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:110">
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
-      <c r="AX2" s="7"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
-      <c r="BB2" s="7"/>
+        <v>107</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF2" s="8"/>
+      <c r="BJ2" s="8"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2" s="3"/>
+      <c r="DF2" s="3"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:49">
+    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:110">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="3">
+        <v>117</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="3">
         <v>94042910</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV3" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>116</v>
-      </c>
+      <c r="K3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="CY3"/>
+      <c r="CZ3"/>
+      <c r="DA3"/>
+      <c r="DB3"/>
+      <c r="DC3"/>
+      <c r="DD3"/>
+      <c r="DE3"/>
+      <c r="DF3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F2">
+  <conditionalFormatting sqref="H2:I2">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
@@ -2086,7 +2131,7 @@
     <cfRule type="duplicateValues" dxfId="1" priority="7"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="J2">
     <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/templates/Item_sample_template.xlsx
+++ b/public/templates/Item_sample_template.xlsx
@@ -352,6 +352,7 @@
 TI - for Traded Item
 A  - for Asset
 E  - for Expense
+SC  - for Scrap
 Leave blank in case of service</t>
   </si>
   <si>

--- a/public/templates/Item_sample_template.xlsx
+++ b/public/templates/Item_sample_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="139">
   <si>
     <t>S.No</t>
   </si>
@@ -41,6 +41,93 @@
     <t>Sub-Type</t>
   </si>
   <si>
+    <t>Item Name</t>
+  </si>
+  <si>
+    <t>Item Code</t>
+  </si>
+  <si>
+    <t>HSN/SAC</t>
+  </si>
+  <si>
+    <t>Inventory UOM</t>
+  </si>
+  <si>
+    <t>Cost Price</t>
+  </si>
+  <si>
+    <t>Cost Price Currency</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
+    <t>Sell Price Currency</t>
+  </si>
+  <si>
+    <t>Min Stocking Level</t>
+  </si>
+  <si>
+    <t>Max Stocking Level</t>
+  </si>
+  <si>
+    <t>Reorder Level</t>
+  </si>
+  <si>
+    <t>Min Order Qty</t>
+  </si>
+  <si>
+    <t>Lead Days</t>
+  </si>
+  <si>
+    <t>Safety Days</t>
+  </si>
+  <si>
+    <t>Shelf Life (Days)</t>
+  </si>
+  <si>
+    <t>PO Positive Tolerance</t>
+  </si>
+  <si>
+    <t>PO Negative Tolerance</t>
+  </si>
+  <si>
+    <t>SO Positive Tolerance</t>
+  </si>
+  <si>
+    <t>SO Negative Tolerance</t>
+  </si>
+  <si>
+    <t>Is Serial No</t>
+  </si>
+  <si>
+    <t>Is Batch No</t>
+  </si>
+  <si>
+    <t>Is Expiry</t>
+  </si>
+  <si>
+    <t>Is Inspection</t>
+  </si>
+  <si>
+    <t>Inspection Checklist</t>
+  </si>
+  <si>
+    <t>Storage UOM</t>
+  </si>
+  <si>
+    <t>Storage UOM Conversion</t>
+  </si>
+  <si>
+    <t>Storage UOM Count</t>
+  </si>
+  <si>
+    <t>Storage Weight</t>
+  </si>
+  <si>
+    <t>Storage Volume</t>
+  </si>
+  <si>
     <t>Asset Category</t>
   </si>
   <si>
@@ -48,57 +135,6 @@
   </si>
   <si>
     <t>Model No</t>
-  </si>
-  <si>
-    <t>Item Name</t>
-  </si>
-  <si>
-    <t>Item Code</t>
-  </si>
-  <si>
-    <t>HSN/SAC</t>
-  </si>
-  <si>
-    <t>Inventory UOM</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Cost Price</t>
-  </si>
-  <si>
-    <t>Sale Price</t>
-  </si>
-  <si>
-    <t>Min Stocking Level</t>
-  </si>
-  <si>
-    <t>Max Stocking Level</t>
-  </si>
-  <si>
-    <t>Reorder Level</t>
-  </si>
-  <si>
-    <t>Min Order Qty</t>
-  </si>
-  <si>
-    <t>Lead Days</t>
-  </si>
-  <si>
-    <t>Safety Days</t>
-  </si>
-  <si>
-    <t>Shelf Life (Days)</t>
-  </si>
-  <si>
-    <t>Expected Life (yrs)</t>
-  </si>
-  <si>
-    <t>Maintenance Schedule</t>
-  </si>
-  <si>
-    <t>Brand Name</t>
   </si>
   <si>
     <t>Alternate UOM 1</t>
@@ -356,6 +392,27 @@
 Leave blank in case of service</t>
   </si>
   <si>
+    <t>Name of the Item</t>
+  </si>
+  <si>
+    <t>Mandatory if manual code is being used</t>
+  </si>
+  <si>
+    <t>HSN/SAC Code</t>
+  </si>
+  <si>
+    <t>UOM of the item</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>Y/N</t>
+  </si>
+  <si>
+    <t>If inspection is ‘Yes’, then checklist is required.</t>
+  </si>
+  <si>
     <t>Asset Category is mandatory when the Sub Type is an asset</t>
   </si>
   <si>
@@ -363,21 +420,6 @@
   </si>
   <si>
     <t>Model No. is mandatory when the Sub Type is an asset.</t>
-  </si>
-  <si>
-    <t>Name of the Item</t>
-  </si>
-  <si>
-    <t>Mandatory if manual code is being used</t>
-  </si>
-  <si>
-    <t>HSN/SAC Code</t>
-  </si>
-  <si>
-    <t>UOM of the item</t>
-  </si>
-  <si>
-    <t>INR</t>
   </si>
   <si>
     <t>P - for Purchase
@@ -388,9 +430,6 @@
   </si>
   <si>
     <t>Comma saperated values or leave blank for All</t>
-  </si>
-  <si>
-    <t>Y/N</t>
   </si>
   <si>
     <t>G</t>
@@ -1686,23 +1725,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:DF3"/>
+  <dimension ref="A1:DX3"/>
   <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9.57407407407407" customWidth="1"/>
     <col min="2" max="2" width="13.4259259259259" customWidth="1"/>
     <col min="3" max="3" width="24.287037037037" customWidth="1"/>
     <col min="4" max="4" width="26.1388888888889" customWidth="1"/>
-    <col min="5" max="8" width="17.8611111111111" customWidth="1"/>
-    <col min="9" max="10" width="15.287037037037" customWidth="1"/>
-    <col min="11" max="11" width="16.712962962963" customWidth="1"/>
-    <col min="12" max="13" width="12.5740740740741" customWidth="1"/>
-    <col min="52" max="52" width="21" customWidth="1"/>
-    <col min="53" max="53" width="17" customWidth="1"/>
-    <col min="56" max="56" width="16.4259259259259" customWidth="1"/>
+    <col min="5" max="5" width="17.8611111111111" customWidth="1"/>
+    <col min="6" max="7" width="15.287037037037" customWidth="1"/>
+    <col min="8" max="8" width="16.712962962963" customWidth="1"/>
+    <col min="9" max="9" width="12.5740740740741" customWidth="1"/>
+    <col min="20" max="20" width="11.2222222222222" customWidth="1"/>
+    <col min="21" max="21" width="11.7777777777778" customWidth="1"/>
+    <col min="22" max="22" width="10.4444444444444" customWidth="1"/>
+    <col min="23" max="23" width="11.2222222222222" customWidth="1"/>
+    <col min="24" max="24" width="10.4444444444444" customWidth="1"/>
+    <col min="25" max="25" width="10.3333333333333" customWidth="1"/>
+    <col min="27" max="27" width="11.3333333333333" customWidth="1"/>
+    <col min="28" max="28" width="9.88888888888889" customWidth="1"/>
+    <col min="30" max="30" width="12.1111111111111" customWidth="1"/>
+    <col min="31" max="31" width="12.7777777777778" customWidth="1"/>
+    <col min="34" max="34" width="10.2222222222222" customWidth="1"/>
+    <col min="35" max="36" width="9.77777777777778" customWidth="1"/>
+    <col min="62" max="62" width="21" customWidth="1"/>
+    <col min="63" max="63" width="17" customWidth="1"/>
+    <col min="66" max="66" width="9.11111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:108">
+    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:118">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1727,22 +1778,22 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="7" t="s">
@@ -1767,363 +1818,427 @@
         <v>20</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AM1" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AN1" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AQ1" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR1" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AS1" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT1" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AU1" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AV1" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AW1" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX1" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AY1" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AZ1" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="BA1" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BB1" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="BC1" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BD1" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="BE1" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BF1" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="BG1" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BH1" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="BI1" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="BJ1" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="BK1" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="BL1" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="BM1" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="BN1" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="BO1" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="BP1" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="BQ1" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BR1" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BS1" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BT1" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BU1" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="BV1" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="BW1" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="BX1" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="BY1" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BZ1" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="CA1" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="CB1" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="CC1" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="CD1" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CF1" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="CG1" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="CH1" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="CI1" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="CJ1" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="CK1" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="CL1" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="CM1" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="CN1" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="CO1" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="CP1" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CQ1" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="CR1" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="CS1" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="CT1" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CV1" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="CW1" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="CY1" s="3"/>
-      <c r="CZ1" s="3"/>
-      <c r="DA1" s="3"/>
-      <c r="DB1" s="3"/>
-      <c r="DC1" s="3"/>
-      <c r="DD1" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="CY1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" s="3"/>
+      <c r="DJ1" s="3"/>
+      <c r="DK1" s="3"/>
+      <c r="DL1" s="3"/>
+      <c r="DM1" s="3"/>
+      <c r="DN1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:110">
+    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:128">
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="BF2" s="8"/>
-      <c r="BJ2" s="8"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2" s="3"/>
-      <c r="DF2" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BP2" s="8"/>
+      <c r="BT2" s="8"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2" s="3"/>
+      <c r="DP2" s="3"/>
+      <c r="DQ2" s="3"/>
+      <c r="DR2" s="3"/>
+      <c r="DS2" s="3"/>
+      <c r="DT2" s="3"/>
+      <c r="DU2" s="3"/>
+      <c r="DV2" s="3"/>
+      <c r="DW2" s="3"/>
+      <c r="DX2"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:110">
+    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:128">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>117</v>
+        <v>130</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="3">
+        <v>94042910</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="3">
-        <v>94042910</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AZ3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BB3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE3" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="CY3"/>
-      <c r="CZ3"/>
-      <c r="DA3"/>
-      <c r="DB3"/>
-      <c r="DC3"/>
-      <c r="DD3"/>
-      <c r="DE3"/>
-      <c r="DF3"/>
+        <v>132</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BK3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="DI3"/>
+      <c r="DJ3"/>
+      <c r="DK3"/>
+      <c r="DL3"/>
+      <c r="DM3"/>
+      <c r="DN3"/>
+      <c r="DO3"/>
+      <c r="DP3"/>
+      <c r="DQ3"/>
+      <c r="DR3"/>
+      <c r="DS3"/>
+      <c r="DT3"/>
+      <c r="DU3"/>
+      <c r="DV3"/>
+      <c r="DW3"/>
+      <c r="DX3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:I2">
+  <conditionalFormatting sqref="E2:F2">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
@@ -2132,7 +2247,7 @@
     <cfRule type="duplicateValues" dxfId="1" priority="7"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
+  <conditionalFormatting sqref="G2">
     <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
